--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E69939D-E420-1C49-AA40-48F0B63B809D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD486E99-BF3E-FD40-B6EE-ED50D785B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="11120" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="35">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -1733,6 +1733,299 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>4</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C88">
+        <v>78.599999999999994</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>16</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C90">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C92">
+        <v>78.099999999999994</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>18</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C95">
+        <v>87.4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C96">
+        <v>76.400000000000006</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C99">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C100">
+        <v>66.400000000000006</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>21</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C103">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C105">
+        <v>76.099999999999994</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>24</v>
+      </c>
+      <c r="B107" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C109">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>26</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>10</v>
+      </c>
+      <c r="B111" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C111">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>27</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>29</v>
+      </c>
+      <c r="B113" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C114">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>31</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C115">
+        <v>87.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>32</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C116">
+        <v>80.400000000000006</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C117">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" s="1">
+        <v>46281</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD486E99-BF3E-FD40-B6EE-ED50D785B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C68B5E-CE2D-494E-AB64-BC36B9D4BE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="11120" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -1751,6 +1751,9 @@
       <c r="B89" s="1">
         <v>46281</v>
       </c>
+      <c r="C89">
+        <v>93.1</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
@@ -1770,6 +1773,9 @@
       <c r="B91" s="1">
         <v>46281</v>
       </c>
+      <c r="C91">
+        <v>89.4</v>
+      </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
@@ -1789,6 +1795,9 @@
       <c r="B93" s="1">
         <v>46281</v>
       </c>
+      <c r="C93">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
@@ -1827,6 +1836,9 @@
       <c r="B97" s="1">
         <v>46281</v>
       </c>
+      <c r="C97">
+        <v>66.3</v>
+      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
@@ -1865,6 +1877,9 @@
       <c r="B101" s="1">
         <v>46281</v>
       </c>
+      <c r="C101">
+        <v>79</v>
+      </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
@@ -1892,6 +1907,9 @@
       <c r="B104" s="1">
         <v>46281</v>
       </c>
+      <c r="C104">
+        <v>70.099999999999994</v>
+      </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
@@ -1919,6 +1937,9 @@
       <c r="B107" s="1">
         <v>46281</v>
       </c>
+      <c r="C107">
+        <v>63.2</v>
+      </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
@@ -1946,6 +1967,9 @@
       <c r="B110" s="1">
         <v>46281</v>
       </c>
+      <c r="C110">
+        <v>82</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
@@ -1964,6 +1988,9 @@
       </c>
       <c r="B112" s="1">
         <v>46281</v>
+      </c>
+      <c r="C112">
+        <v>80.3</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C68B5E-CE2D-494E-AB64-BC36B9D4BE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ABE563-4553-9948-94B6-0AD8556FD44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="11120" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -207,6 +207,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1715,6 +1716,9 @@
       <c r="A86" t="s">
         <v>33</v>
       </c>
+      <c r="B86" s="1">
+        <v>46252</v>
+      </c>
       <c r="C86">
         <v>70.2</v>
       </c>
@@ -1726,6 +1730,9 @@
       <c r="A87" t="s">
         <v>34</v>
       </c>
+      <c r="B87" s="1">
+        <v>46252</v>
+      </c>
       <c r="C87">
         <v>88.9</v>
       </c>
@@ -1743,6 +1750,9 @@
       <c r="C88">
         <v>78.599999999999994</v>
       </c>
+      <c r="D88" s="7">
+        <v>7.1999999999999995E-2</v>
+      </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
@@ -1754,6 +1764,9 @@
       <c r="C89">
         <v>93.1</v>
       </c>
+      <c r="D89" s="7">
+        <v>0.115</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
@@ -1765,6 +1778,9 @@
       <c r="C90">
         <v>82.7</v>
       </c>
+      <c r="D90" s="7">
+        <v>7.8E-2</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
@@ -1776,6 +1792,9 @@
       <c r="C91">
         <v>89.4</v>
       </c>
+      <c r="D91" s="7">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
@@ -1787,6 +1806,9 @@
       <c r="C92">
         <v>78.099999999999994</v>
       </c>
+      <c r="D92" s="7">
+        <v>6.2E-2</v>
+      </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
@@ -1798,6 +1820,9 @@
       <c r="C93">
         <v>81.2</v>
       </c>
+      <c r="D93" s="7">
+        <v>4.8000000000000001E-2</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
@@ -1806,6 +1831,7 @@
       <c r="B94" s="1">
         <v>46281</v>
       </c>
+      <c r="D94" s="7"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
@@ -1817,6 +1843,9 @@
       <c r="C95">
         <v>87.4</v>
       </c>
+      <c r="D95" s="7">
+        <v>7.1999999999999995E-2</v>
+      </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
@@ -1828,8 +1857,11 @@
       <c r="C96">
         <v>76.400000000000006</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D96" s="7">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -1839,16 +1871,20 @@
       <c r="C97">
         <v>66.3</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D97" s="7">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>8</v>
       </c>
       <c r="B98" s="1">
         <v>46281</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D98" s="7"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>14</v>
       </c>
@@ -1858,8 +1894,11 @@
       <c r="C99">
         <v>74.3</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D99" s="7">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>9</v>
       </c>
@@ -1869,8 +1908,11 @@
       <c r="C100">
         <v>66.400000000000006</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D100" s="7">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>20</v>
       </c>
@@ -1880,16 +1922,20 @@
       <c r="C101">
         <v>79</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D101" s="7">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>21</v>
       </c>
       <c r="B102" s="1">
         <v>46281</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D102" s="7"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -1899,8 +1945,11 @@
       <c r="C103">
         <v>72.7</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D103" s="7">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -1910,8 +1959,11 @@
       <c r="C104">
         <v>70.099999999999994</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D104" s="7">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -1921,16 +1973,20 @@
       <c r="C105">
         <v>76.099999999999994</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D105" s="7">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>23</v>
       </c>
       <c r="B106" s="1">
         <v>46281</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D106" s="7"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>24</v>
       </c>
@@ -1940,16 +1996,20 @@
       <c r="C107">
         <v>63.2</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D107" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>25</v>
       </c>
       <c r="B108" s="1">
         <v>46281</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D108" s="7"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>28</v>
       </c>
@@ -1959,8 +2019,11 @@
       <c r="C109">
         <v>69.2</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D109" s="7">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>26</v>
       </c>
@@ -1970,8 +2033,11 @@
       <c r="C110">
         <v>82</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D110" s="7">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -1981,8 +2047,11 @@
       <c r="C111">
         <v>66.5</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D111" s="7">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>27</v>
       </c>
@@ -1992,16 +2061,20 @@
       <c r="C112">
         <v>80.3</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D112" s="7">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>29</v>
       </c>
       <c r="B113" s="1">
         <v>46281</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D113" s="7"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>30</v>
       </c>
@@ -2011,8 +2084,11 @@
       <c r="C114">
         <v>73.8</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D114" s="7">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>31</v>
       </c>
@@ -2022,8 +2098,11 @@
       <c r="C115">
         <v>87.1</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D115" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>32</v>
       </c>
@@ -2033,8 +2112,11 @@
       <c r="C116">
         <v>80.400000000000006</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D116" s="7">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>33</v>
       </c>
@@ -2044,14 +2126,18 @@
       <c r="C117">
         <v>70.2</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D117" s="7">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>34</v>
       </c>
       <c r="B118" s="1">
         <v>46281</v>
       </c>
+      <c r="D118" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ABE563-4553-9948-94B6-0AD8556FD44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15787DE-5C50-1B47-B145-2C691692096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="13420" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="35">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -2139,6 +2139,266 @@
       </c>
       <c r="D118" s="7"/>
     </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C119">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>16</v>
+      </c>
+      <c r="B121" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>6</v>
+      </c>
+      <c r="B122" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>17</v>
+      </c>
+      <c r="B124" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>18</v>
+      </c>
+      <c r="B125" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>12</v>
+      </c>
+      <c r="B126" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>7</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>20</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>21</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>13</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C136">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>23</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>24</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C139">
+        <v>71.400000000000006</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>26</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>10</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>27</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>29</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>30</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>31</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C146">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>32</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>33</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>34</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46314</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15787DE-5C50-1B47-B145-2C691692096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C7731D-78EA-F74A-90DE-9438857FBDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13420" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="10880" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -2181,6 +2180,9 @@
       <c r="B123" s="1">
         <v>46314</v>
       </c>
+      <c r="C123">
+        <v>78.599999999999994</v>
+      </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
@@ -2205,6 +2207,9 @@
       <c r="B126" s="1">
         <v>46314</v>
       </c>
+      <c r="C126">
+        <v>87.1</v>
+      </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
@@ -2253,6 +2258,9 @@
       <c r="B132" s="1">
         <v>46314</v>
       </c>
+      <c r="C132">
+        <v>79.5</v>
+      </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
@@ -2296,6 +2304,9 @@
       <c r="B137" s="1">
         <v>46314</v>
       </c>
+      <c r="C137">
+        <v>63.9</v>
+      </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
@@ -2304,6 +2315,9 @@
       <c r="B138" s="1">
         <v>46314</v>
       </c>
+      <c r="C138">
+        <v>60.9</v>
+      </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
@@ -2355,6 +2369,9 @@
       <c r="B144" s="1">
         <v>46314</v>
       </c>
+      <c r="C144">
+        <v>58</v>
+      </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
@@ -2397,6 +2414,9 @@
       </c>
       <c r="B149" s="1">
         <v>46314</v>
+      </c>
+      <c r="C149">
+        <v>88.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C7731D-78EA-F74A-90DE-9438857FBDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8E6E64-7FB3-544C-80DC-CF24DA86A236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10880" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="36">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -140,6 +141,9 @@
   </si>
   <si>
     <t>Marc Thomas</t>
+  </si>
+  <si>
+    <t>Jeremy Romany</t>
   </si>
 </sst>
 </file>
@@ -541,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -2156,6 +2160,9 @@
       <c r="B120" s="1">
         <v>46314</v>
       </c>
+      <c r="C120">
+        <v>92.3</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
@@ -2172,6 +2179,9 @@
       <c r="B122" s="1">
         <v>46314</v>
       </c>
+      <c r="C122">
+        <v>89.1</v>
+      </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
@@ -2191,6 +2201,9 @@
       <c r="B124" s="1">
         <v>46314</v>
       </c>
+      <c r="C124">
+        <v>80.099999999999994</v>
+      </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
@@ -2345,6 +2358,9 @@
       <c r="B141" s="1">
         <v>46314</v>
       </c>
+      <c r="C141">
+        <v>81.599999999999994</v>
+      </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
@@ -2380,6 +2396,9 @@
       <c r="B145" s="1">
         <v>46314</v>
       </c>
+      <c r="C145">
+        <v>73</v>
+      </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
@@ -2407,6 +2426,9 @@
       <c r="B148" s="1">
         <v>46314</v>
       </c>
+      <c r="C148">
+        <v>71.400000000000006</v>
+      </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
@@ -2417,6 +2439,17 @@
       </c>
       <c r="C149">
         <v>88.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>35</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C150">
+        <v>88.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8E6E64-7FB3-544C-80DC-CF24DA86A236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAC19FF-8AD6-B641-AFF1-DCB7ECEEA075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10880" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -2255,6 +2255,9 @@
       <c r="B130" s="1">
         <v>46314</v>
       </c>
+      <c r="C130">
+        <v>75.2</v>
+      </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
@@ -2281,6 +2284,9 @@
       </c>
       <c r="B133" s="1">
         <v>46314</v>
+      </c>
+      <c r="C133">
+        <v>70.8</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAC19FF-8AD6-B641-AFF1-DCB7ECEEA075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D79A6DD-9910-734D-8E2F-AD39BA1D8981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10880" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="37">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Jeremy Romany</t>
+  </si>
+  <si>
+    <t>Glenn Manga-Tabi</t>
   </si>
 </sst>
 </file>
@@ -545,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -2239,6 +2242,9 @@
       <c r="B128" s="1">
         <v>46314</v>
       </c>
+      <c r="C128">
+        <v>66.2</v>
+      </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
@@ -2456,6 +2462,17 @@
       </c>
       <c r="C150">
         <v>88.8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>36</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C151">
+        <v>90.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D79A6DD-9910-734D-8E2F-AD39BA1D8981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA65B8F-1433-634E-88DA-ECC2E2E5B7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10880" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2234,6 +2234,9 @@
       <c r="B127" s="1">
         <v>46314</v>
       </c>
+      <c r="C127">
+        <v>79</v>
+      </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
@@ -2271,6 +2274,9 @@
       </c>
       <c r="B131" s="1">
         <v>46314</v>
+      </c>
+      <c r="C131">
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">

--- a/data/2026-2027/Poids-Masse grasse.xlsx
+++ b/data/2026-2027/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA65B8F-1433-634E-88DA-ECC2E2E5B7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9672FD66-5781-3840-958E-0D19B2156FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="10880" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="37">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -548,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -2155,6 +2155,9 @@
       <c r="C119">
         <v>78</v>
       </c>
+      <c r="D119" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
@@ -2166,6 +2169,9 @@
       <c r="C120">
         <v>92.3</v>
       </c>
+      <c r="D120" s="7">
+        <v>9.2999999999999999E-2</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
@@ -2174,6 +2180,7 @@
       <c r="B121" s="1">
         <v>46314</v>
       </c>
+      <c r="D121" s="7"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
@@ -2185,6 +2192,9 @@
       <c r="C122">
         <v>89.1</v>
       </c>
+      <c r="D122" s="7">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
@@ -2196,6 +2206,9 @@
       <c r="C123">
         <v>78.599999999999994</v>
       </c>
+      <c r="D123" s="7">
+        <v>7.1999999999999995E-2</v>
+      </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
@@ -2207,6 +2220,9 @@
       <c r="C124">
         <v>80.099999999999994</v>
       </c>
+      <c r="D124" s="7">
+        <v>5.1999999999999998E-2</v>
+      </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
@@ -2215,6 +2231,7 @@
       <c r="B125" s="1">
         <v>46314</v>
       </c>
+      <c r="D125" s="7"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
@@ -2226,6 +2243,9 @@
       <c r="C126">
         <v>87.1</v>
       </c>
+      <c r="D126" s="7">
+        <v>7.8E-2</v>
+      </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
@@ -2237,6 +2257,9 @@
       <c r="C127">
         <v>79</v>
       </c>
+      <c r="D127" s="7">
+        <v>4.8000000000000001E-2</v>
+      </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
@@ -2248,16 +2271,20 @@
       <c r="C128">
         <v>66.2</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D128" s="7">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>8</v>
       </c>
       <c r="B129" s="1">
         <v>46314</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D129" s="7"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>14</v>
       </c>
@@ -2267,8 +2294,11 @@
       <c r="C130">
         <v>75.2</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D130" s="7">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -2278,8 +2308,11 @@
       <c r="C131">
         <v>67.099999999999994</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D131" s="7">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>20</v>
       </c>
@@ -2289,8 +2322,11 @@
       <c r="C132">
         <v>79.5</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D132" s="7">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>21</v>
       </c>
@@ -2300,24 +2336,29 @@
       <c r="C133">
         <v>70.8</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D133" s="7">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>22</v>
       </c>
       <c r="B134" s="1">
         <v>46314</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D134" s="7"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>13</v>
       </c>
       <c r="B135" s="1">
         <v>46314</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D135" s="7"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -2327,8 +2368,11 @@
       <c r="C136">
         <v>77.5</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D136" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>23</v>
       </c>
@@ -2338,8 +2382,11 @@
       <c r="C137">
         <v>63.9</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D137" s="7">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -2349,8 +2396,11 @@
       <c r="C138">
         <v>60.9</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D138" s="7">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -2360,16 +2410,20 @@
       <c r="C139">
         <v>71.400000000000006</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D139" s="7">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>28</v>
       </c>
       <c r="B140" s="1">
         <v>46314</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D140" s="7"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -2379,24 +2433,29 @@
       <c r="C141">
         <v>81.599999999999994</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D141" s="7">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>10</v>
       </c>
       <c r="B142" s="1">
         <v>46314</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D142" s="7"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>27</v>
       </c>
       <c r="B143" s="1">
         <v>46314</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D143" s="7"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>29</v>
       </c>
@@ -2406,8 +2465,11 @@
       <c r="C144">
         <v>58</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D144" s="7">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>30</v>
       </c>
@@ -2417,8 +2479,11 @@
       <c r="C145">
         <v>73</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D145" s="7">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>31</v>
       </c>
@@ -2428,57 +2493,64 @@
       <c r="C146">
         <v>87.3</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D146" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B147" s="1">
         <v>46314</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C147">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="D147" s="7">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B148" s="1">
         <v>46314</v>
       </c>
       <c r="C148">
-        <v>71.400000000000006</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+        <v>88.5</v>
+      </c>
+      <c r="D148" s="7">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B149" s="1">
         <v>46314</v>
       </c>
       <c r="C149">
-        <v>88.5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+        <v>88.8</v>
+      </c>
+      <c r="D149" s="7">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B150" s="1">
         <v>46314</v>
       </c>
       <c r="C150">
-        <v>88.8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>36</v>
-      </c>
-      <c r="B151" s="1">
-        <v>46314</v>
-      </c>
-      <c r="C151">
         <v>90.6</v>
+      </c>
+      <c r="D150" s="7">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
